--- a/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/productImportSchema_de.xlsx
+++ b/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/productImportSchema_de.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krna/Projects/mes/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lupo/qcadoo-src/mes/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A779EF0-A2EF-B044-BC9D-2459EDA22D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797724A8-611B-8746-A907-2C3F5D52E716}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="8600" windowWidth="28800" windowHeight="9400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="9740" windowWidth="33600" windowHeight="9400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Number</t>
   </si>
@@ -85,16 +85,13 @@
   </si>
   <si>
     <t>Durability</t>
-  </si>
-  <si>
-    <t>Expiration date evidence</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -109,13 +106,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,10 +137,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -811,9 +800,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office 2013–2022">
+    <a:clrScheme name="Pakiet Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -851,7 +840,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office 2013–2022">
+    <a:fontScheme name="Pakiet Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -957,7 +946,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office 2013–2022">
+    <a:fmtScheme name="Pakiet Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1099,7 +1088,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1107,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="16.83203125" customWidth="1"/>
@@ -1117,7 +1106,7 @@
     <col min="16" max="18" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1171,9 +1160,6 @@
       </c>
       <c r="R1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
